--- a/Test Scenarios/Test scripts/UNICORN - TR-18 SR H5 mobile web.xlsx
+++ b/Test Scenarios/Test scripts/UNICORN - TR-18 SR H5 mobile web.xlsx
@@ -1292,7 +1292,7 @@
     <row r="2">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>단계 9 — 결함: 상세의 환자 정보에 전화만 있고 성명이 빈 칸이다 (목록에는 (E)김감기로 보인다)</t>
+          <t>단계 9 — 상세의 환자 정보에 성명 (E)김감기 와 전화가 함께 선다 (고친 뒤 다시 수행)</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>CE Admin 2026-10-10 build (bc2e50cf)</t>
+          <t>CE Admin 2026-10-10 build (d27612b4)</t>
         </is>
       </c>
       <c r="D3" s="11" t="n"/>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Test Finished: Failed</t>
+          <t>Test Finished: Passed</t>
         </is>
       </c>
       <c r="C9" s="11" t="n"/>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="203.2941176470588" customHeight="1">
+    <row r="23" ht="261.4632352941176" customHeight="1">
       <c r="A23" s="10" t="n">
         <v>9</v>
       </c>
@@ -2430,12 +2430,12 @@
       </c>
       <c r="E23" s="28" t="inlineStr">
         <is>
-          <t>/m/prescriptions/RX-20261010-001 shows RX-20261010-001 · 검수 필요 and 「등록 서류 1건 · 처방전 · rx_처방전.jpg」 with the image, so the document arrived. DEFECT: 「환자 정보」 shows only 전화 — 성명 is missing, although the same case shows (E)김감기 in the list one screen earlier. Cause read from the source: the detail endpoint builds 성명 from patient_name_ocr alone (PrescriptionApiController::formatOcrResult, line 897), while the list and the lookup read the linked patient first ($p-&gt;patient?-&gt;name ?? $p-&gt;patient_name_ocr, lines 386 and 546). A case uploaded through H5 or the app, where the patient is picked from the registry, has patient_name_ocr empty (RX-20261010-001: patient_id=12986, patient_name_ocr=NULL), so the name disappears on the detail screen. The two cases of 2026-09-30 are not affected because their patient_name_ocr is filled. The same endpoint feeds the SR mobile app, so the app shows the same gap. The operator sees a case with a phone number and no name.</t>
+          <t>/m/prescriptions/RX-20261010-001 shows RX-20261010-001 · 검수 필요, 「등록 서류 1건 · 처방전 · rx_처방전.jpg」 with the image, and 「환자 정보」 with 성명 = (E)김감기 and the mobile number — the name is the patient that was picked on the upload screen, the same name the list shows. DEFECT FOUND AND FIXED DURING THIS RUN: on the first execution 성명 was blank and only 전화 was shown. Cause read from the source: the detail endpoint built 성명 from patient_name_ocr alone (PrescriptionApiController::formatOcrResult, line 897), while the list and the lookup read the linked patient first ($p-&gt;patient?-&gt;name ?? $p-&gt;patient_name_ocr, lines 386 and 546). A case uploaded through H5 or the app has patient_name_ocr empty because the patient is picked from the registry and createWith() does not fill that column (RX-20261010-001: patient_id=12986, patient_name_ocr=NULL), so the name disappeared on the detail screen only. The same endpoint feeds the SR mobile app, so the app showed the same gap. Fixed in commit d27612b4 ($p-&gt;patient_name_ocr ?: $p-&gt;patient?-&gt;name), deployed to both servers and re-executed: the detail now answers patient_name=(E)김감기 for this case, and the two cases of 2026-09-30, whose patient_name_ocr is filled, still answer their own OCR value — no regression.</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="G23" s="33" t="inlineStr">

--- a/Test Scenarios/Test scripts/UNICORN - TR-18 SR H5 mobile web.xlsx
+++ b/Test Scenarios/Test scripts/UNICORN - TR-18 SR H5 mobile web.xlsx
@@ -2329,7 +2329,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="108" customHeight="1">
+    <row r="21" ht="124.4779411764706" customHeight="1">
       <c r="A21" s="10" t="n">
         <v>7</v>
       </c>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="E21" s="28" t="inlineStr">
         <is>
-          <t>Pressed 업로드. The screen answered 「처방전 RX-20261010-001 에 1건을 등록했습니다.」 and cleared itself — the patient, the document queue and the memo were all empty afterwards. No message was sent by the upload itself: the automatic SMS fires on the first save of the detail list, not on upload (PrescriptionController:3058), so nothing left the system for this step.</t>
+          <t>Pressed 업로드. The screen answered 「처방전 RX-20261010-001 에 1건을 등록했습니다.」 and cleared itself — the patient, the document queue and the memo were all empty afterwards. The message clears itself after a few seconds, so the capture on Doc step 07 was taken on a repeat of the same action a few minutes later, which answered 「처방전 RX-20261010-002 에 1건을 등록했습니다.」 in the same way. No message was sent by the upload itself: the automatic SMS fires on the first save of the detail list, not on upload (PrescriptionController:3058), so nothing left the system for this step.</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -2698,7 +2698,7 @@
     <row r="2">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>단계 7 — 업로드 성공 · 「처방전 RX-20261010-001 에 1건을 등록했습니다」, 화면이 스스로 비워짐</t>
+          <t>단계 7 — 업로드 성공 · 「처방전 RX-20261010-002 에 1건을 등록했습니다」, 화면이 스스로 비워짐 (같은 동작 반복 촬영)</t>
         </is>
       </c>
     </row>

--- a/Test Scenarios/Test scripts/UNICORN - TR-18 SR H5 mobile web.xlsx
+++ b/Test Scenarios/Test scripts/UNICORN - TR-18 SR H5 mobile web.xlsx
@@ -1270,7 +1270,7 @@
     <row r="2">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>단계 8 — 목록에 RX-20261010-001 · 검수 필요 · (E)김감기 · 2026-10-10 14:22</t>
+          <t>단계 8 — 목록에 RX-20261010-001 · 검수 필요 · (E)이원형 · 2026-10-10 15:34</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
     <row r="2">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>단계 9 — 상세의 환자 정보에 성명 (E)김감기 와 전화가 함께 선다 (고친 뒤 다시 수행)</t>
+          <t>단계 9 — 상세에 등록 서류 1건과 환자 정보의 성명 (E)이원형 이 함께 선다</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
     <row r="2">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>단계 10 — 설정 · 내 정보와 공지사항 · 알림 이력 · 문의하기, 앱 판 v1.3.2, 로그아웃</t>
+          <t>단계 10 — 설정 · 내 정보와 공지사항 · 알림 이력 · 문의하기, 앱 판 v1.3.5, 로그아웃</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>UNICORN Test (https://ceadmin.co.kr)</t>
+          <t>UNICORN Production</t>
         </is>
       </c>
       <c r="C2" s="11" t="n"/>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>CE Admin 2026-10-10 build (d27612b4)</t>
+          <t>CE Admin 2026-10-10 build (e96cc6fe)</t>
         </is>
       </c>
       <c r="D3" s="11" t="n"/>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>This document defines the test scenarios used to verify the SR H5 mobile web, the web-built replacement for the SR mobile app. It covers the phone-browser screens under /m: sign-in, the "my prescriptions" list with its status chips and upload-date filter, the prescription lookup by name and date of birth (cases uploaded by another member of staff), the case detail with its documents, the upload flow (patient search, document type, per-type limits, attach and remove, submit) and the settings screen with notices, notification history and enquiries. The H5 screens call the same /api/* endpoints as the mobile app and are authenticated by the web session, so this test also covers that the session is accepted on the address the staff actually open.</t>
+          <t>This document defines the test scenarios used to verify the SR H5 mobile web, the web-built replacement for the SR mobile app. It covers the phone-browser screens under /m: sign-in, the "my prescriptions" list with its status chips and upload-date filter, the prescription lookup by name and date of birth (cases uploaded by another member of staff), the case detail with its documents and OCR result, the upload flow (patient search, document type, per-type limits, attach and remove, submit) and the settings screen with notices, notification history and enquiries. The H5 screens call the same /api/* endpoints as the mobile app and are authenticated by the web session, so this test also covers that the session is accepted on the address the staff actually open.</t>
         </is>
       </c>
       <c r="C5" s="11" t="n"/>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>A CE Admin account that may upload. A phone browser with no CE Admin session. The test patient (E)김감기 (date of birth 1987-02-02) exists in CE Admin, and two cases uploaded by other members of staff exist for that patient on 2026-09-30. A prescription image file on the phone.</t>
+          <t>A CE Admin account that may upload. A phone browser with no CE Admin session. The test patient (E)이원형 (date of birth 1956-09-01) exists in CE Admin, and the case RX-20261008-070 for that patient, uploaded by another member of staff (Mia Kim), is in status 검수 필요 with two documents. A prescription image file on the phone.</t>
         </is>
       </c>
       <c r="C11" s="9" t="n"/>
@@ -2089,18 +2089,18 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="178.0808823529412" customHeight="1">
+    <row r="15" ht="186.8161764705882" customHeight="1">
       <c r="A15" s="10" t="n">
         <v>1</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Open https://ceadmin.co.kr/m/login in a phone browser with no CE Admin session, and sign in.</t>
+          <t>Open https://75.2.99.52/m/login in a phone browser with no CE Admin session, and sign in.</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
         <is>
-          <t>https://ceadmin.co.kr/m/login</t>
+          <t>https://75.2.99.52/m/login</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="E15" s="28" t="inlineStr">
         <is>
-          <t>Opened https://ceadmin.co.kr/m/login in a phone-sized browser (360 x 780, DPR 3) with no CE Admin session. The screen shows "Coloplast CE Admin / 의료기기 주문 · 청구 관리", the 「Microsoft 계정으로 로그인」 button with 「임직원은 Microsoft 계정(Entra ID)으로 로그인해 주십시오」, and below it 「또는 이메일로 로그인」 with e-mail and password and 「로그인 후 SMS 인증번호가 발송됩니다.」 The operator signed in. /m opens 「내 처방전」 (page title 내 처방전). This also verifies the defect found and fixed on 2026-10-10: signing in on this address previously landed on the web dashboard, because /api/* answered 401 on the host without "www" and the screen then sent the browser to /m/login, which redirects a signed-in person to route("dashboard"). After the fix (commit bc2e50cf) /api/auth/me answers 200, /m redirects to /m/prescriptions and /m/login redirects a signed-in person to /m/prescriptions.</t>
+          <t>Opened https://75.2.99.52/m/login in a phone-sized browser (360 x 780, DPR 3) with no CE Admin session. The screen shows "Coloplast CE Admin / 의료기기 주문 · 청구 관리", the 「Microsoft 계정으로 로그인」 button with 「임직원은 Microsoft 계정(Entra ID)으로 로그인해 주십시오」, and below it 「또는 이메일로 로그인」 with e-mail and password and 「로그인 후 SMS 인증번호가 발송됩니다.」 The operator signed in. /m opens 「내 처방전」 (page title 내 처방전) and /api/auth/me answers 200 for the signed-in account. This also confirms the defect corrected on 2026-10-10 (commit bc2e50cf): on a host that was not listed as a stateful Sanctum domain the /api endpoints refused the web session with 401, the screen then sent the browser to /m/login, and /m/login redirects a signed-in person to route("dashboard") — so the phone showed the web dashboard. /m now redirects to /m/prescriptions and /m/login redirects a signed-in person to /m/prescriptions.</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
@@ -2129,13 +2129,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="146.1176470588235" customHeight="1">
+    <row r="16" ht="109.7867647058824" customHeight="1">
       <c r="A16" s="10" t="n">
         <v>2</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Filter the list by upload date 2026-09-30 and by the status chips.</t>
+          <t>Filter the list by upload date 2026-09-30 and check the status chips.</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="E16" s="28" t="inlineStr">
         <is>
-          <t>The header reads 「본인이 등록한 처방전」 and the chips are 전체 / 검수 필요 / 검수 요청 / 검수 보류 / 검수 완료 / 반려 / 주문 완료. Setting the range to 2026-09-30 ~ 2026-09-30 reloaded the list and it answered 「등록한 처방전이 없습니다.」 That is correct, not a defect: this account holds exactly one case of that date in the test database (RX-20260930-003) and it is an empty draft with no document, which the list hides on purpose (PrescriptionApiController::index, the blankDraft / counselOnly rule added 2026-09-27 so that the app and the web list hide the same rows). /api/prescriptions answered total 0 for the same range. The reset control next to the range appears as soon as the range is not the default.</t>
+          <t>The header reads 「본인이 등록한 처방전」 and the chips are 전체 / 검수 필요 / 검수 요청 / 검수 보류 / 검수 완료 / 반려 / 주문 완료. Setting the range to 2026-09-30 ~ 2026-09-30 reloaded the list and it answered 「등록한 처방전이 없습니다.」 That is correct: all 73 prescriptions of that date in production are records migrated from WITHWORKS (WW-ADD…) with no uploader, and this account uploaded none of them, so none belong in "my prescriptions". The reset control next to the range appears as soon as the range is not the default.</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Name: (E)김감기 · Date of birth: 19870202</t>
+          <t>Name: (E)이원형 · Date of birth: 19560901</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="E17" s="28" t="inlineStr">
         <is>
-          <t>「처방전 조회」 states 「이름과 생년월일이 모두 일치해야 조회됩니다. 생년월일은 숫자 8자리나 주민등록번호 앞자리로도 됩니다. 다른 담당자가 등록한 처방전에도 서류를 추가할 수 있습니다.」 Searching (E)김감기 with 19870202 returned the two cases of 2026-09-30 that other staff uploaded: RX-20260930-011 (대기 중 · 서류 0장 · 등록자 May park) and RX-20260930-004 (대기 중 · 서류 0장 · 등록자 Stella Kim). Date of birth 1987-02-02 is shown on each row so the operator can tell one person from another.</t>
+          <t>「처방전 조회」 states 「이름과 생년월일이 모두 일치해야 조회됩니다. 생년월일은 숫자 8자리나 주민등록번호 앞자리로도 됩니다. 다른 담당자가 등록한 처방전에도 서류를 추가할 수 있습니다.」 Searching (E)이원형 with 19560901 returned RX-20261008-070 — 검수 필요 · (E)이원형 · 1956-09-01 · 서류 2장 · 등록자: Mia Kim. The date of birth is shown on the row so the operator can tell one person from another.</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -2209,7 +2209,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="108" customHeight="1">
+    <row r="18" ht="139.5661764705882" customHeight="1">
       <c r="A18" s="10" t="n">
         <v>4</v>
       </c>
@@ -2220,17 +2220,17 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>RX-20260930-011</t>
+          <t>RX-20261008-070</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>The detail shows the prescription number, the status, the documents, who uploaded it, and states that documents may be added but only one’s own documents may be deleted.</t>
+          <t>The detail shows the prescription number, the status, the documents, who uploaded it, the patient, the hospital and prescription details, and states that documents may be added but only one’s own documents may be deleted.</t>
         </is>
       </c>
       <c r="E18" s="28" t="inlineStr">
         <is>
-          <t>/m/prescriptions/RX-20260930-011 opened (page title 처방전 상세). It shows RX-20260930-011 · 대기 중, 「등록 서류 0건 · 등록된 서류가 없습니다.」, the notice 「May park 님이 등록한 처방전입니다. 서류를 추가할 수 있으며, 본인이 등록한 서류만 삭제할 수 있습니다.」, a 「서류 추가」 control (카메라 / 사진 선택) and 「환자 정보」 with 성명 = (E)김감기 and the mobile number. The API answers editable=false, can_add=true, is_mine=false, owner_name="May park", so the screen and the server agree on what this account may do.</t>
+          <t>/m/prescriptions/RX-20261008-070 opened (page title 처방전 상세). It shows RX-20261008-070 · 검수 필요, 「등록 서류 2건」 — 처방전 KakaoTalk_20261008_180317000.jpg and 등록신청서 KakaoTalk_20261008_180204450.jpg with thumbnails — the notice 「Mia Kim 님이 등록한 처방전입니다. 서류를 추가할 수 있으며, 본인이 등록한 서류만 삭제할 수 있습니다.」, a 「서류 추가」 control, and the read data: 환자 정보 (성명 (E)이원형), 의료기관 (인제대학교일산백병원 · 31100651 · 이건철 · 비뇨기과 · 면허번호 52910), 상병 정보 (방광의 상세불명의 신경근육기능장애 · N31.9) and 처방 내용 (1일 횟수 6 · 총 일수 90 · 총 수량 540 · 발급일 2026-10-07). The API answers editable=false, can_add=true, is_mine=false, owner_name="Mia Kim", so the screen and the server agree on what this account may do.</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Name: (E)김감기</t>
+          <t>Name: (E)이원형</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="E19" s="28" t="inlineStr">
         <is>
-          <t>/m/upload (page title 처방전 업로드). Searching (E)김감기 listed 「이미 등록된 환자 1명」 with 「생년월일로 동일인 여부를 확인한 뒤 선택해 주십시오.」, the row (E)김감기 · 1987-02-02 · mobile number, and 「해당 환자가 없습니다 — 신규 등록」. Picking the row showed 「(E)김감기 님 선택됨」. The register-new sheet asks for the resident registration number and was not used in this test.</t>
+          <t>/m/upload (page title 처방전 업로드). Searching (E)이원형 listed 「이미 등록된 환자 2명」 with 「생년월일로 동일인 여부를 확인한 뒤 선택해 주십시오.」 — (E)이원형 · 1956-09-01 · 01072207042 and (E)이원형A · 생년월일 없음 · 01088399556 — and 「해당 환자가 없습니다 — 신규 등록」. Two people share almost the same name, which is exactly the case the date of birth is there to separate. Picking the first row showed 「(E)이원형 님 선택됨」. The register-new sheet asks for the resident registration number and was not used in this test.</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -2289,28 +2289,28 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="160.610294117647" customHeight="1">
+    <row r="20" ht="130.0367647058823" customHeight="1">
       <c r="A20" s="10" t="n">
         <v>6</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Attach documents by switching the document type, check the per-type limit, then remove one.</t>
+          <t>Attach a document by switching the document type, and check the per-type limit.</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Document types: 처방전 / 등록신청서 / 결과지 / 신분증 / 개인정보 동의서 / 기타</t>
+          <t>Document types: 등록신청서 / 처방전 / 결과지 / 신분증 / 요양비청구서(서명본) / 개인정보 동의서 / 기타</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Each file is added under the type that is selected at the time. A second file of a type whose limit is 1 is refused with a message and the count does not change. A file can be removed before submitting.</t>
+          <t>Each file is added under the type that is selected at the time. A second file of a type whose limit is 1 is refused with a message and the count does not change.</t>
         </is>
       </c>
       <c r="E20" s="28" t="inlineStr">
         <is>
-          <t>The type list came from /api/prescriptions/doc-types: 처방전(prescription), 등록신청서(registration_form), 결과지(test_result), 신분증(id_card), 개인정보 동의서(privacy_consent), 기타(other). The type the screen starts on is 등록신청서, as in the mobile app, and the screen says so in words (「등록신청서로 추가합니다」), so the operator can see it must be changed to upload a prescription. Set to 처방전 and attached rx_처방전.jpg — it appeared under 「추가된 서류 1건」 as 처방전 with its file name. Attaching a second 처방전 was refused at once with 「처방전은 한 번에 1건까지 업로드할 수 있습니다.」 and the count stayed at 1건 — the same limit the web upload enforces. Switching the type to 기타 and attaching the second file made it 2건, and the 빼기 (x) control on that row brought it back to 1건, leaving 처방전 / rx_처방전.jpg.</t>
+          <t>The type list came from /api/prescriptions/doc-types and holds seven types in production: 등록신청서 / 처방전 / 결과지 / 신분증 / 요양비청구서(서명본) / 개인정보 동의서 / 기타. The type the screen starts on is 등록신청서, as in the mobile app, and the screen says so in words (「등록신청서로 추가합니다」), so the operator can see it must be changed to upload a prescription. Set to 처방전 and attached rx_처방전.jpg — it appeared under 「추가된 서류 1건」 as 처방전 with its file name and a 빼기 (x) control. Attaching a second 처방전 was refused at once with 「처방전은 한 번에 1건까지 업로드할 수 있습니다.」 and the count stayed at 1건 — the same limit the web upload enforces.</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -2329,7 +2329,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="124.4779411764706" customHeight="1">
+    <row r="21" ht="108" customHeight="1">
       <c r="A21" s="10" t="n">
         <v>7</v>
       </c>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="E21" s="28" t="inlineStr">
         <is>
-          <t>Pressed 업로드. The screen answered 「처방전 RX-20261010-001 에 1건을 등록했습니다.」 and cleared itself — the patient, the document queue and the memo were all empty afterwards. The message clears itself after a few seconds, so the capture on Doc step 07 was taken on a repeat of the same action a few minutes later, which answered 「처방전 RX-20261010-002 에 1건을 등록했습니다.」 in the same way. No message was sent by the upload itself: the automatic SMS fires on the first save of the detail list, not on upload (PrescriptionController:3058), so nothing left the system for this step.</t>
+          <t>Pressed 업로드. The screen answered 「처방전 RX-20261010-001 에 1건을 등록했습니다.」 and cleared itself — the patient, the document queue (0건) and the memo were all empty afterwards. The record was created with created_by = the signed-in account, upload_source = mobile and the memo that was typed. No message was sent by the upload itself: the automatic SMS fires on the first save of the detail list, not on upload (PrescriptionController:3058), so nothing left the system for this step.</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Query date: 2026-10-10 (default)</t>
+          <t>Query date: 2026-10-10 (default) · chip 검수 필요</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="E22" s="28" t="inlineStr">
         <is>
-          <t>The list header became 「본인이 등록한 처방전 1건」 and the row reads RX-20261010-001 · 검수 필요 · (E)김감기 · 2026-10-10 14:22. Pressing the 검수 필요 chip kept the row.</t>
+          <t>The list header became 「본인이 등록한 처방전 1건」 and the row reads RX-20261010-001 · 검수 필요 · (E)이원형 · 2026-10-10 15:34. Pressing the 검수 필요 chip kept the row.</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -2409,7 +2409,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="261.4632352941176" customHeight="1">
+    <row r="23" ht="223.9411764705882" customHeight="1">
       <c r="A23" s="10" t="n">
         <v>9</v>
       </c>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="E23" s="28" t="inlineStr">
         <is>
-          <t>/m/prescriptions/RX-20261010-001 shows RX-20261010-001 · 검수 필요, 「등록 서류 1건 · 처방전 · rx_처방전.jpg」 with the image, and 「환자 정보」 with 성명 = (E)김감기 and the mobile number — the name is the patient that was picked on the upload screen, the same name the list shows. DEFECT FOUND AND FIXED DURING THIS RUN: on the first execution 성명 was blank and only 전화 was shown. Cause read from the source: the detail endpoint built 성명 from patient_name_ocr alone (PrescriptionApiController::formatOcrResult, line 897), while the list and the lookup read the linked patient first ($p-&gt;patient?-&gt;name ?? $p-&gt;patient_name_ocr, lines 386 and 546). A case uploaded through H5 or the app has patient_name_ocr empty because the patient is picked from the registry and createWith() does not fill that column (RX-20261010-001: patient_id=12986, patient_name_ocr=NULL), so the name disappeared on the detail screen only. The same endpoint feeds the SR mobile app, so the app showed the same gap. Fixed in commit d27612b4 ($p-&gt;patient_name_ocr ?: $p-&gt;patient?-&gt;name), deployed to both servers and re-executed: the detail now answers patient_name=(E)김감기 for this case, and the two cases of 2026-09-30, whose patient_name_ocr is filled, still answer their own OCR value — no regression.</t>
+          <t>/m/prescriptions/RX-20261010-001 shows RX-20261010-001 · 검수 필요, 「등록 서류 1건 · 처방전 · rx_처방전.jpg」 with the image, and 「환자 정보」 with 성명 = (E)이원형 and the contact number — the patient that was picked on the upload screen, the same name the list shows. This step failed when it was first executed on 2026-10-10 and the defect was corrected before this run: the detail endpoint built 성명 from patient_name_ocr alone (PrescriptionApiController::formatOcrResult, line 897) while the list and the lookup read the linked patient first (lines 386 and 546), so a case uploaded from the mobile screens — where the patient is picked from the registry and createWith() leaves patient_name_ocr empty — showed a phone number and no name. The same endpoint feeds the SR mobile app. Fixed in commit d27612b4 ($p-&gt;patient_name_ocr ?: $p-&gt;patient?-&gt;name). Verified on this production record, which has patient_name_ocr = NULL and patient_id = 1641: the screen and the API both answer (E)이원형. Cases whose patient_name_ocr is filled still answer their own OCR value, so nothing regressed.</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -2449,7 +2449,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="155.25" customHeight="1">
+    <row r="24" ht="108" customHeight="1">
       <c r="A24" s="10" t="n">
         <v>10</v>
       </c>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
-          <t>/m/settings shows the account (관리자 · admin@ce-admin.co.kr), 서비스 with 공지사항 (/m/notices), 알림 이력 (/m/notifications) and 문의하기 (/m/inquiries), 앱 정보 Coloplast CE Admin v1.3.2, and 계정 › 로그아웃. 공지사항 answered 「총 0개 · 공지사항이 없습니다.」 (none are registered in the test database), 알림 이력 listed the real notification history (re-upload requests with patient, document type and reason), and 문의하기 answered 「총 0개」 with 문의 등록하기, whose form offers 유형 (구매 / 처방전 / 앱 이용 / 기타), 제목, 내용 and 파일 첨부. The 채팅 tab is not on the bottom bar because the server setting hides it (chat_hidden = 1); the bar therefore holds 처방전 / 업로드 / 설정. 로그아웃 was not pressed, so that the session used for this test run was kept — the control is present on the screen.</t>
+          <t>/m/settings shows the signed-in account, 서비스 with 공지사항 (/m/notices), 알림 이력 (/m/notifications) and 문의하기 (/m/inquiries), 앱 정보 Coloplast CE Admin v1.3.5, and 계정 › 로그아웃. The 채팅 tab is not on the bottom bar because the server setting hides it (chat_hidden = 1); the bar therefore holds 처방전 / 업로드 / 설정. 로그아웃 was not pressed, so that the session used for this test run was kept — the control is present on the screen.</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -2588,7 +2588,7 @@
     <row r="2">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>단계 2 — 조회일 2026-09-30 · 본인이 등록한 것이 없어 빈 목록 (빈 초안은 잣대대로 감춰진다)</t>
+          <t>단계 2 — 조회일 2026-09-30 · 본인이 등록한 것이 없어 빈 목록 (그날 73건은 모두 위드웍스에서 옮겨 온 자료)</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
     <row r="2">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>단계 3 — 처방전 조회 · 이름+생년월일로 다른 담당자가 올린 2026-09-30 두 건을 찾음</t>
+          <t>단계 3 — 처방전 조회 · 이름+생년월일로 Mia Kim 이 올린 RX-20261008-070 을 찾음</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
     <row r="2">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>단계 4 — 남이 올린 건의 상세 · 등록자와 「서류는 추가할 수 있고 본인 것만 지울 수 있다」 안내</t>
+          <t>단계 4 — 남이 올린 건의 상세 · 서류 2장과 등록자 안내, 환자 정보와 의료기관이 함께 보임</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
     <row r="2">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>단계 5 — 업로드 · 이름으로 찾아 생년월일로 가려 고르는 환자 목록</t>
+          <t>단계 5 — 업로드 · 이름이 거의 같은 두 사람을 생년월일로 가려 고른다</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
     <row r="2">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>단계 7 — 업로드 성공 · 「처방전 RX-20261010-002 에 1건을 등록했습니다」, 화면이 스스로 비워짐 (같은 동작 반복 촬영)</t>
+          <t>단계 7 — 업로드 성공 · 「처방전 RX-20261010-001 에 1건을 등록했습니다」, 화면이 스스로 비워짐</t>
         </is>
       </c>
     </row>

--- a/Test Scenarios/Test scripts/UNICORN - TR-18 SR H5 mobile web.xlsx
+++ b/Test Scenarios/Test scripts/UNICORN - TR-18 SR H5 mobile web.xlsx
@@ -2120,14 +2120,10 @@
       </c>
       <c r="G15" s="33" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>jack won</t>
-        </is>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="n"/>
     </row>
     <row r="16" ht="109.7867647058824" customHeight="1">
       <c r="A16" s="10" t="n">
@@ -2160,14 +2156,10 @@
       </c>
       <c r="G16" s="33" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>jack won</t>
-        </is>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="n"/>
     </row>
     <row r="17" ht="108" customHeight="1">
       <c r="A17" s="10" t="n">
@@ -2200,14 +2192,10 @@
       </c>
       <c r="G17" s="33" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>jack won</t>
-        </is>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="n"/>
     </row>
     <row r="18" ht="139.5661764705882" customHeight="1">
       <c r="A18" s="10" t="n">
@@ -2240,14 +2228,10 @@
       </c>
       <c r="G18" s="33" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>jack won</t>
-        </is>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="n"/>
     </row>
     <row r="19" ht="108" customHeight="1">
       <c r="A19" s="10" t="n">
@@ -2280,14 +2264,10 @@
       </c>
       <c r="G19" s="33" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>jack won</t>
-        </is>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n"/>
     </row>
     <row r="20" ht="130.0367647058823" customHeight="1">
       <c r="A20" s="10" t="n">
@@ -2320,14 +2300,10 @@
       </c>
       <c r="G20" s="33" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>jack won</t>
-        </is>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="n"/>
     </row>
     <row r="21" ht="108" customHeight="1">
       <c r="A21" s="10" t="n">
@@ -2360,14 +2336,10 @@
       </c>
       <c r="G21" s="33" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>jack won</t>
-        </is>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="n"/>
     </row>
     <row r="22" ht="108" customHeight="1">
       <c r="A22" s="10" t="n">
@@ -2400,14 +2372,10 @@
       </c>
       <c r="G22" s="33" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>jack won</t>
-        </is>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="n"/>
     </row>
     <row r="23" ht="223.9411764705882" customHeight="1">
       <c r="A23" s="10" t="n">
@@ -2440,14 +2408,10 @@
       </c>
       <c r="G23" s="33" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>jack won</t>
-        </is>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="n"/>
     </row>
     <row r="24" ht="108" customHeight="1">
       <c r="A24" s="10" t="n">
@@ -2480,14 +2444,10 @@
       </c>
       <c r="G24" s="33" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>jack won</t>
-        </is>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="2" t="n"/>

--- a/Test Scenarios/Test scripts/UNICORN - TR-18 SR H5 mobile web.xlsx
+++ b/Test Scenarios/Test scripts/UNICORN - TR-18 SR H5 mobile web.xlsx
@@ -1270,7 +1270,7 @@
     <row r="2">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>단계 8 — 목록에 RX-20261010-001 · 검수 필요 · (E)이원형 · 2026-10-10 15:34</t>
+          <t>단계 8 — 「1건을 업로드했습니다」 · 같은 건에 등록 서류 1건이 붙음 (새 건이 서지 않는다)</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
     <row r="2">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>단계 9 — 상세에 등록 서류 1건과 환자 정보의 성명 (E)이원형 이 함께 선다</t>
+          <t>단계 9 — 다시 조회하면 RX-20260930-011 이 서류 1장, RX-20260930-004 는 0장 그대로</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
     <row r="2">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>단계 10 — 설정 · 내 정보와 공지사항 · 알림 이력 · 문의하기, 앱 판 v1.3.5, 로그아웃</t>
+          <t>단계 10 — 설정 · 내 정보와 공지사항 · 알림 이력 · 문의하기, 앱 판 v1.3.2, 로그아웃</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>UNICORN Production</t>
+          <t>UNICORN Test (https://ceadmin.co.kr)</t>
         </is>
       </c>
       <c r="C2" s="11" t="n"/>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>CE Admin 2026-10-10 build (e96cc6fe)</t>
+          <t>CE Admin 2026-09-30 build</t>
         </is>
       </c>
       <c r="D3" s="11" t="n"/>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>This document defines the test scenarios used to verify the SR H5 mobile web, the web-built replacement for the SR mobile app. It covers the phone-browser screens under /m: sign-in, the "my prescriptions" list with its status chips and upload-date filter, the prescription lookup by name and date of birth (cases uploaded by another member of staff), the case detail with its documents and OCR result, the upload flow (patient search, document type, per-type limits, attach and remove, submit) and the settings screen with notices, notification history and enquiries. The H5 screens call the same /api/* endpoints as the mobile app and are authenticated by the web session, so this test also covers that the session is accepted on the address the staff actually open.</t>
+          <t>This document defines the test scenarios used to verify the SR H5 mobile web, the web-built replacement for the SR mobile app. It covers the phone-browser screens under /m: sign-in, the "my prescriptions" list with its status chips and upload-date filter, the prescription lookup by name and date of birth (cases uploaded by another member of staff), the case detail with its documents and patient information, adding documents to a case from the detail screen (including the rule that a prescription may only be added by the member of staff who created the case, and the per-type limit), the upload screen with its patient search, and the settings screen with notices, notification history and enquiries. The H5 screens call the same /api/* endpoints as the mobile app and are authenticated by the web session, so this test also covers that the session is accepted on the address the staff actually open.</t>
         </is>
       </c>
       <c r="C5" s="11" t="n"/>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>A CE Admin account that may upload. A phone browser with no CE Admin session. The test patient (E)이원형 (date of birth 1956-09-01) exists in CE Admin, and the case RX-20261008-070 for that patient, uploaded by another member of staff (Mia Kim), is in status 검수 필요 with two documents. A prescription image file on the phone.</t>
+          <t>A CE Admin account that may upload. A phone browser with no CE Admin session. The test patient (E)김감기 (date of birth 1987-02-02) exists in CE Admin, and two cases for that patient uploaded by other members of staff on 2026-09-30 — RX-20260930-011 (May park) and RX-20260930-004 (Stella Kim) — are in status 대기 중 with no documents. A document image file on the phone.</t>
         </is>
       </c>
       <c r="C11" s="9" t="n"/>
@@ -2089,18 +2089,18 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="186.8161764705882" customHeight="1">
+    <row r="15" ht="191.9779411764706" customHeight="1">
       <c r="A15" s="10" t="n">
         <v>1</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Open https://75.2.99.52/m/login in a phone browser with no CE Admin session, and sign in.</t>
+          <t>Open https://ceadmin.co.kr/m/login in a phone browser with no CE Admin session, and sign in.</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
         <is>
-          <t>https://75.2.99.52/m/login</t>
+          <t>https://ceadmin.co.kr/m/login</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="E15" s="28" t="inlineStr">
         <is>
-          <t>Opened https://75.2.99.52/m/login in a phone-sized browser (360 x 780, DPR 3) with no CE Admin session. The screen shows "Coloplast CE Admin / 의료기기 주문 · 청구 관리", the 「Microsoft 계정으로 로그인」 button with 「임직원은 Microsoft 계정(Entra ID)으로 로그인해 주십시오」, and below it 「또는 이메일로 로그인」 with e-mail and password and 「로그인 후 SMS 인증번호가 발송됩니다.」 The operator signed in. /m opens 「내 처방전」 (page title 내 처방전) and /api/auth/me answers 200 for the signed-in account. This also confirms the defect corrected on 2026-10-10 (commit bc2e50cf): on a host that was not listed as a stateful Sanctum domain the /api endpoints refused the web session with 401, the screen then sent the browser to /m/login, and /m/login redirects a signed-in person to route("dashboard") — so the phone showed the web dashboard. /m now redirects to /m/prescriptions and /m/login redirects a signed-in person to /m/prescriptions.</t>
+          <t>Opened https://ceadmin.co.kr/m/login in a phone-sized browser (360 x 780, DPR 3) with no CE Admin session. The screen shows "Coloplast CE Admin / 의료기기 주문 · 청구 관리", the 「Microsoft 계정으로 로그인」 button with 「임직원은 Microsoft 계정(Entra ID)으로 로그인해 주십시오」, and below it 「또는 이메일로 로그인」 with e-mail and password and 「로그인 후 SMS 인증번호가 발송됩니다.」 The operator signed in. /m opens 「내 처방전」 (page title 내 처방전) and /api/auth/me answers 200 for the signed-in account. This also confirms a defect that was found and corrected during the preparation of this script: on a host that was not listed as a stateful Sanctum domain the /api endpoints refused the web session with 401, the screen then sent the browser to /m/login, and /m/login redirects a signed-in person to route("dashboard") — so the phone showed the web dashboard. /m now redirects to /m/prescriptions and /m/login redirects a signed-in person to /m/prescriptions.</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="H15" s="8" t="n"/>
     </row>
-    <row r="16" ht="109.7867647058824" customHeight="1">
+    <row r="16" ht="124.0808823529412" customHeight="1">
       <c r="A16" s="10" t="n">
         <v>2</v>
       </c>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E16" s="28" t="inlineStr">
         <is>
-          <t>The header reads 「본인이 등록한 처방전」 and the chips are 전체 / 검수 필요 / 검수 요청 / 검수 보류 / 검수 완료 / 반려 / 주문 완료. Setting the range to 2026-09-30 ~ 2026-09-30 reloaded the list and it answered 「등록한 처방전이 없습니다.」 That is correct: all 73 prescriptions of that date in production are records migrated from WITHWORKS (WW-ADD…) with no uploader, and this account uploaded none of them, so none belong in "my prescriptions". The reset control next to the range appears as soon as the range is not the default.</t>
+          <t>The header reads 「본인이 등록한 처방전」 and the chips are 전체 / 검수 필요 / 검수 요청 / 검수 보류 / 검수 완료 / 반려 / 주문 완료. Setting the range to 2026-09-30 ~ 2026-09-30 reloaded the list and it answered 「등록한 처방전이 없습니다.」 That is correct, not a defect: this account holds exactly one case of that date and it is an empty draft with no document, which the list hides on purpose (PrescriptionApiController::index, the blankDraft / counselOnly rule, so that the app and the web list hide the same rows). The reset control next to the range appears as soon as the range is not the default.</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Name: (E)이원형 · Date of birth: 19560901</t>
+          <t>Name: (E)김감기 · Date of birth: 19870202</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="E17" s="28" t="inlineStr">
         <is>
-          <t>「처방전 조회」 states 「이름과 생년월일이 모두 일치해야 조회됩니다. 생년월일은 숫자 8자리나 주민등록번호 앞자리로도 됩니다. 다른 담당자가 등록한 처방전에도 서류를 추가할 수 있습니다.」 Searching (E)이원형 with 19560901 returned RX-20261008-070 — 검수 필요 · (E)이원형 · 1956-09-01 · 서류 2장 · 등록자: Mia Kim. The date of birth is shown on the row so the operator can tell one person from another.</t>
+          <t>「처방전 조회」 states 「이름과 생년월일이 모두 일치해야 조회됩니다. 생년월일은 숫자 8자리나 주민등록번호 앞자리로도 됩니다. 다른 담당자가 등록한 처방전에도 서류를 추가할 수 있습니다.」 Searching (E)김감기 with 19870202 returned the two cases of 2026-09-30 that other staff uploaded: RX-20260930-011 (대기 중 · 서류 0장 · 등록자 May park) and RX-20260930-004 (대기 중 · 서류 0장 · 등록자 Stella Kim). The date of birth is shown on each row so the operator can tell one person from another.</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="H17" s="8" t="n"/>
     </row>
-    <row r="18" ht="139.5661764705882" customHeight="1">
+    <row r="18" ht="108" customHeight="1">
       <c r="A18" s="10" t="n">
         <v>4</v>
       </c>
@@ -2208,17 +2208,17 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>RX-20261008-070</t>
+          <t>RX-20260930-011</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>The detail shows the prescription number, the status, the documents, who uploaded it, the patient, the hospital and prescription details, and states that documents may be added but only one’s own documents may be deleted.</t>
+          <t>The detail shows the prescription number, the status, the documents, who uploaded it and the patient information, and states that documents may be added but only one’s own documents may be deleted.</t>
         </is>
       </c>
       <c r="E18" s="28" t="inlineStr">
         <is>
-          <t>/m/prescriptions/RX-20261008-070 opened (page title 처방전 상세). It shows RX-20261008-070 · 검수 필요, 「등록 서류 2건」 — 처방전 KakaoTalk_20261008_180317000.jpg and 등록신청서 KakaoTalk_20261008_180204450.jpg with thumbnails — the notice 「Mia Kim 님이 등록한 처방전입니다. 서류를 추가할 수 있으며, 본인이 등록한 서류만 삭제할 수 있습니다.」, a 「서류 추가」 control, and the read data: 환자 정보 (성명 (E)이원형), 의료기관 (인제대학교일산백병원 · 31100651 · 이건철 · 비뇨기과 · 면허번호 52910), 상병 정보 (방광의 상세불명의 신경근육기능장애 · N31.9) and 처방 내용 (1일 횟수 6 · 총 일수 90 · 총 수량 540 · 발급일 2026-10-07). The API answers editable=false, can_add=true, is_mine=false, owner_name="Mia Kim", so the screen and the server agree on what this account may do.</t>
+          <t>/m/prescriptions/RX-20260930-011 opened (page title 처방전 상세). It shows RX-20260930-011 · 대기 중, 「등록 서류 0건 · 등록된 서류가 없습니다.」, the notice 「May park 님이 등록한 처방전입니다. 서류를 추가할 수 있으며, 본인이 등록한 서류만 삭제할 수 있습니다.」, a 「서류 추가」 control and 「환자 정보」 with 성명 = (E)김감기 and the contact number. The API answers editable=false, can_add=true, is_mine=false, owner_name="May park", so the screen and the server agree on what this account may do.</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -2233,28 +2233,28 @@
       </c>
       <c r="H18" s="8" t="n"/>
     </row>
-    <row r="19" ht="108" customHeight="1">
+    <row r="19" ht="131.2279411764706" customHeight="1">
       <c r="A19" s="10" t="n">
         <v>5</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>On the upload screen, search the patient by name and pick the right person by date of birth.</t>
+          <t>On the upload screen, search the patient by name and check the selection rule.</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Name: (E)이원형</t>
+          <t>Name: (E)김감기</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>The already-registered patients are listed with their date of birth and contact number, with the notice that the date of birth decides who the person is, and a "no such patient — register" entry. Picking one shows 「… 님 선택됨」.</t>
+          <t>The already-registered patients are listed with their date of birth and contact number, with the notice that the date of birth decides who the person is, and a "no such patient — register" entry.</t>
         </is>
       </c>
       <c r="E19" s="28" t="inlineStr">
         <is>
-          <t>/m/upload (page title 처방전 업로드). Searching (E)이원형 listed 「이미 등록된 환자 2명」 with 「생년월일로 동일인 여부를 확인한 뒤 선택해 주십시오.」 — (E)이원형 · 1956-09-01 · 01072207042 and (E)이원형A · 생년월일 없음 · 01088399556 — and 「해당 환자가 없습니다 — 신규 등록」. Two people share almost the same name, which is exactly the case the date of birth is there to separate. Picking the first row showed 「(E)이원형 님 선택됨」. The register-new sheet asks for the resident registration number and was not used in this test.</t>
+          <t>/m/upload (page title 처방전 업로드). The document type the screen starts on is 등록신청서 and it says so in words (「등록신청서로 추가합니다」), so the operator can see it must be changed to upload a prescription. Searching (E)김감기 listed 「이미 등록된 환자 1명」 with 「생년월일로 동일인 여부를 확인한 뒤 선택해 주십시오.」, the row (E)김감기 · 1987-02-02 · contact number, and 「해당 환자가 없습니다 — 신규 등록」. The register-new sheet asks for the resident registration number and was not used in this test. This screen always opens a NEW case, so the documents in this run were added to the existing 2026-09-30 case from its detail screen instead (step 6 onward).</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -2269,28 +2269,28 @@
       </c>
       <c r="H19" s="8" t="n"/>
     </row>
-    <row r="20" ht="130.0367647058823" customHeight="1">
+    <row r="20" ht="108" customHeight="1">
       <c r="A20" s="10" t="n">
         <v>6</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Attach a document by switching the document type, and check the per-type limit.</t>
+          <t>Open 「서류 추가」 on a case created by another member of staff.</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Document types: 등록신청서 / 처방전 / 결과지 / 신분증 / 요양비청구서(서명본) / 개인정보 동의서 / 기타</t>
+          <t>RX-20260930-011 (created by May park)</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Each file is added under the type that is selected at the time. A second file of a type whose limit is 1 is refused with a message and the count does not change.</t>
+          <t>A prescription may only be added by the member of staff who created the case. The type list must therefore leave 처방전 out and the screen must say so.</t>
         </is>
       </c>
       <c r="E20" s="28" t="inlineStr">
         <is>
-          <t>The type list came from /api/prescriptions/doc-types and holds seven types in production: 등록신청서 / 처방전 / 결과지 / 신분증 / 요양비청구서(서명본) / 개인정보 동의서 / 기타. The type the screen starts on is 등록신청서, as in the mobile app, and the screen says so in words (「등록신청서로 추가합니다」), so the operator can see it must be changed to upload a prescription. Set to 처방전 and attached rx_처방전.jpg — it appeared under 「추가된 서류 1건」 as 처방전 with its file name and a 빼기 (x) control. Attaching a second 처방전 was refused at once with 「처방전은 한 번에 1건까지 업로드할 수 있습니다.」 and the count stayed at 1건 — the same limit the web upload enforces.</t>
+          <t>On RX-20260930-011 the 「서류 추가」 sheet offered 등록신청서 / 결과지 / 신분증 / 개인정보 동의서 / 기타 — **처방전 is not offered** — with the notice 「처방전은 May park 님만 등록할 수 있습니다. 그 외 서류는 추가할 수 있습니다.」 and the instruction 「RX-20260930-011에 추가할 서류 유형을 선택해 주십시오. 목록에 추가한 뒤 아래 「서류 업로드」로 한 번에 업로드합니다.」 The rule is enforced on the screen the operator sees, not only on the server.</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -2311,22 +2311,22 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Submit the upload.</t>
+          <t>Add a document and check the per-type limit.</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>1 document (처방전) and an operator memo</t>
+          <t>Type 등록신청서 · one image file, then a second of the same type</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>The upload succeeds, a prescription number RX-YYYYMMDD-NNN is issued and the screen clears itself (patient, documents, memo and document type all reset).</t>
+          <t>The file is added to the waiting list under the type that is selected. A second file of a type whose limit is 1 is refused with a message and the count does not change.</t>
         </is>
       </c>
       <c r="E21" s="28" t="inlineStr">
         <is>
-          <t>Pressed 업로드. The screen answered 「처방전 RX-20261010-001 에 1건을 등록했습니다.」 and cleared itself — the patient, the document queue (0건) and the memo were all empty afterwards. The record was created with created_by = the signed-in account, upload_source = mobile and the memo that was typed. No message was sent by the upload itself: the automatic SMS fires on the first save of the detail list, not on upload (PrescriptionController:3058), so nothing left the system for this step.</t>
+          <t>Chose 등록신청서 and attached an image — it appeared under 「업로드 대기 서류 1건」 with 「아래 「서류 업로드」를 선택하면 한 번에 업로드됩니다.」, the file name and a remove (x) control, and the button became 「서류 업로드 (1건)」. Attaching a second 등록신청서 was refused at once with 「등록신청서는 1건만 업로드할 수 있습니다.」 and the count stayed at 1건 — the same limit the app and the web upload enforce.</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -2347,22 +2347,22 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Check the uploaded case in the list.</t>
+          <t>Upload the waiting document.</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Query date: 2026-10-10 (default) · chip 검수 필요</t>
+          <t>「서류 업로드 (1건)」</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>The case appears with status 「검수 필요」 and stays when the 「검수 필요」 chip is used.</t>
+          <t>The upload succeeds, the waiting list is cleared and the document appears under 「등록 서류」 on the same case — no new case is created.</t>
         </is>
       </c>
       <c r="E22" s="28" t="inlineStr">
         <is>
-          <t>The list header became 「본인이 등록한 처방전 1건」 and the row reads RX-20261010-001 · 검수 필요 · (E)이원형 · 2026-10-10 15:34. Pressing the 검수 필요 chip kept the row.</t>
+          <t>Pressed 「서류 업로드 (1건)」. The screen answered 「1건을 업로드했습니다.」 and reloaded the case: 「등록 서류 1건 · 등록신청서 · rx_처방전.jpg」 with a thumbnail and a delete control (this account added it, so it may delete it). The case kept its own number RX-20260930-011 and its own date — the upload is attached to the existing case, not to a new one (the request carries rx_number).</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -2377,28 +2377,28 @@
       </c>
       <c r="H22" s="8" t="n"/>
     </row>
-    <row r="23" ht="223.9411764705882" customHeight="1">
+    <row r="23" ht="108" customHeight="1">
       <c r="A23" s="10" t="n">
         <v>9</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Open the uploaded case and read the patient information on the detail screen.</t>
+          <t>Look the case up again and check that the document count changed.</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>RX-20261010-001</t>
+          <t>Name: (E)김감기 · Date of birth: 19870202</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>The detail shows the document that was uploaded, and the patient information shows the name of the patient that was picked on the upload screen.</t>
+          <t>The looked-up row shows the new document count.</t>
         </is>
       </c>
       <c r="E23" s="28" t="inlineStr">
         <is>
-          <t>/m/prescriptions/RX-20261010-001 shows RX-20261010-001 · 검수 필요, 「등록 서류 1건 · 처방전 · rx_처방전.jpg」 with the image, and 「환자 정보」 with 성명 = (E)이원형 and the contact number — the patient that was picked on the upload screen, the same name the list shows. This step failed when it was first executed on 2026-10-10 and the defect was corrected before this run: the detail endpoint built 성명 from patient_name_ocr alone (PrescriptionApiController::formatOcrResult, line 897) while the list and the lookup read the linked patient first (lines 386 and 546), so a case uploaded from the mobile screens — where the patient is picked from the registry and createWith() leaves patient_name_ocr empty — showed a phone number and no name. The same endpoint feeds the SR mobile app. Fixed in commit d27612b4 ($p-&gt;patient_name_ocr ?: $p-&gt;patient?-&gt;name). Verified on this production record, which has patient_name_ocr = NULL and patient_id = 1641: the screen and the API both answer (E)이원형. Cases whose patient_name_ocr is filled still answer their own OCR value, so nothing regressed.</t>
+          <t>Searching (E)김감기 with 19870202 again returned RX-20260930-011 — 대기 중 · (E)김감기 · 1987-02-02 · **서류 1장** · 등록자 May park — and RX-20260930-004 unchanged at 서류 0장. The document added in step 8 is counted on the case that received it and on no other.</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
-          <t>/m/settings shows the signed-in account, 서비스 with 공지사항 (/m/notices), 알림 이력 (/m/notifications) and 문의하기 (/m/inquiries), 앱 정보 Coloplast CE Admin v1.3.5, and 계정 › 로그아웃. The 채팅 tab is not on the bottom bar because the server setting hides it (chat_hidden = 1); the bar therefore holds 처방전 / 업로드 / 설정. 로그아웃 was not pressed, so that the session used for this test run was kept — the control is present on the screen.</t>
+          <t>/m/settings shows the signed-in account, 서비스 with 공지사항 (/m/notices), 알림 이력 (/m/notifications) and 문의하기 (/m/inquiries), 앱 정보 Coloplast CE Admin v1.3.2, and 계정 › 로그아웃. The 채팅 tab is not on the bottom bar because the server setting hides it (chat_hidden = 1); the bar therefore holds 처방전 / 업로드 / 설정. 로그아웃 was not pressed, so that the session used for this test run was kept — the control is present on the screen.</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -2548,7 +2548,7 @@
     <row r="2">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>단계 2 — 조회일 2026-09-30 · 본인이 등록한 것이 없어 빈 목록 (그날 73건은 모두 위드웍스에서 옮겨 온 자료)</t>
+          <t>단계 2 — 조회일 2026-09-30 · 본인이 등록한 것이 없어 빈 목록 (빈 초안은 잣대대로 감춰진다)</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2570,7 @@
     <row r="2">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>단계 3 — 처방전 조회 · 이름+생년월일로 Mia Kim 이 올린 RX-20261008-070 을 찾음</t>
+          <t>단계 3 — 처방전 조회 · 이름+생년월일로 2026-09-30 두 건을 찾음 (서류 0장)</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
     <row r="2">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>단계 4 — 남이 올린 건의 상세 · 서류 2장과 등록자 안내, 환자 정보와 의료기관이 함께 보임</t>
+          <t>단계 4 — 남이 올린 건의 상세 · 등록자 안내와 환자 정보(성명 (E)김감기)</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
     <row r="2">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>단계 5 — 업로드 · 이름이 거의 같은 두 사람을 생년월일로 가려 고른다</t>
+          <t>단계 5 — 업로드 화면 · 이름으로 찾아 생년월일로 가려 고르는 환자 목록</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
     <row r="2">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>단계 6 — 같은 유형 두 장은 바로 막힌다 · 「처방전은 한 번에 1건까지」, 세지는 수는 1건 그대로</t>
+          <t>단계 6 — 서류 추가 · 남의 건이라 처방전 유형이 없고 「처방전은 May park 님만 등록할 수 있습니다」</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
     <row r="2">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>단계 7 — 업로드 성공 · 「처방전 RX-20261010-001 에 1건을 등록했습니다」, 화면이 스스로 비워짐</t>
+          <t>단계 7 — 같은 유형 두 장은 막힌다 · 「등록신청서는 1건만 업로드할 수 있습니다」, 대기 1건 그대로</t>
         </is>
       </c>
     </row>

--- a/Test Scenarios/Test scripts/UNICORN - TR-18 SR H5 mobile web.xlsx
+++ b/Test Scenarios/Test scripts/UNICORN - TR-18 SR H5 mobile web.xlsx
@@ -1912,7 +1912,7 @@
       </c>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>CE Admin 2026-09-30 build</t>
+          <t>CE Admin 2026-10-10 build</t>
         </is>
       </c>
       <c r="D3" s="11" t="n"/>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>A CE Admin account that may upload. A phone browser with no CE Admin session. The test patient (E)김감기 (date of birth 1987-02-02) exists in CE Admin, and two cases for that patient uploaded by other members of staff on 2026-09-30 — RX-20260930-011 (May park) and RX-20260930-004 (Stella Kim) — are in status 대기 중 with no documents. A document image file on the phone.</t>
+          <t>A CE Admin account that may upload. A phone browser with no CE Admin session. The test patient the test patient exists in CE Admin, and two cases for that patient uploaded by other members of staff on 2026-09-30 — RX-20260930-011 (May park) and RX-20260930-004 (Stella Kim) — are in status 대기 중 with no documents. A document image file on the phone.</t>
         </is>
       </c>
       <c r="C11" s="9" t="n"/>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="G15" s="33" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="H15" s="8" t="n"/>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="G16" s="33" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="H16" s="8" t="n"/>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Name: (E)김감기 · Date of birth: 19870202</t>
+          <t>The test patient: name + date of birth</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="E17" s="28" t="inlineStr">
         <is>
-          <t>「처방전 조회」 states 「이름과 생년월일이 모두 일치해야 조회됩니다. 생년월일은 숫자 8자리나 주민등록번호 앞자리로도 됩니다. 다른 담당자가 등록한 처방전에도 서류를 추가할 수 있습니다.」 Searching (E)김감기 with 19870202 returned the two cases of 2026-09-30 that other staff uploaded: RX-20260930-011 (대기 중 · 서류 0장 · 등록자 May park) and RX-20260930-004 (대기 중 · 서류 0장 · 등록자 Stella Kim). The date of birth is shown on each row so the operator can tell one person from another.</t>
+          <t>「처방전 조회」 states 「이름과 생년월일이 모두 일치해야 조회됩니다. 생년월일은 숫자 8자리나 주민등록번호 앞자리로도 됩니다. 다른 담당자가 등록한 처방전에도 서류를 추가할 수 있습니다.」 Searching the test patient by name and date of birth returned the two cases of 2026-09-30 that other staff uploaded: RX-20260930-011 (대기 중 · 서류 0장 · 등록자 May park) and RX-20260930-004 (대기 중 · 서류 0장 · 등록자 Stella Kim). The date of birth is shown on each row so the operator can tell one person from another.</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G17" s="33" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="H17" s="8" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E18" s="28" t="inlineStr">
         <is>
-          <t>/m/prescriptions/RX-20260930-011 opened (page title 처방전 상세). It shows RX-20260930-011 · 대기 중, 「등록 서류 0건 · 등록된 서류가 없습니다.」, the notice 「May park 님이 등록한 처방전입니다. 서류를 추가할 수 있으며, 본인이 등록한 서류만 삭제할 수 있습니다.」, a 「서류 추가」 control and 「환자 정보」 with 성명 = (E)김감기 and the contact number. The API answers editable=false, can_add=true, is_mine=false, owner_name="May park", so the screen and the server agree on what this account may do.</t>
+          <t>/m/prescriptions/RX-20260930-011 opened (page title 처방전 상세). It shows RX-20260930-011 · 대기 중, 「등록 서류 0건 · 등록된 서류가 없습니다.」, the notice 「May park 님이 등록한 처방전입니다. 서류를 추가할 수 있으며, 본인이 등록한 서류만 삭제할 수 있습니다.」, a 「서류 추가」 control and 「환자 정보」 with 성명 and the contact number. The API answers editable=false, can_add=true, is_mine=false, owner_name="May park", so the screen and the server agree on what this account may do.</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="G18" s="33" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="H18" s="8" t="n"/>
     </row>
-    <row r="19" ht="131.2279411764706" customHeight="1">
+    <row r="19" ht="136.5882352941177" customHeight="1">
       <c r="A19" s="10" t="n">
         <v>5</v>
       </c>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Name: (E)김감기</t>
+          <t>The test patient: name</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="E19" s="28" t="inlineStr">
         <is>
-          <t>/m/upload (page title 처방전 업로드). The document type the screen starts on is 등록신청서 and it says so in words (「등록신청서로 추가합니다」), so the operator can see it must be changed to upload a prescription. Searching (E)김감기 listed 「이미 등록된 환자 1명」 with 「생년월일로 동일인 여부를 확인한 뒤 선택해 주십시오.」, the row (E)김감기 · 1987-02-02 · contact number, and 「해당 환자가 없습니다 — 신규 등록」. The register-new sheet asks for the resident registration number and was not used in this test. This screen always opens a NEW case, so the documents in this run were added to the existing 2026-09-30 case from its detail screen instead (step 6 onward).</t>
+          <t>/m/upload (page title 처방전 업로드). The document type the screen starts on is 등록신청서 and it says so in words (「등록신청서로 추가합니다」), so the operator can see it must be changed to upload a prescription. Searching the test patient by name listed 「이미 등록된 환자 1명」 with 「생년월일로 동일인 여부를 확인한 뒤 선택해 주십시오.」, the row with the date of birth and the contact number, and 「해당 환자가 없습니다 — 신규 등록」. The register-new sheet asks for the resident registration number and was not used in this test. This screen always opens a NEW case, so the documents in this run were added to the existing 2026-09-30 case from its detail screen instead (step 6 onward).</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G19" s="33" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="H19" s="8" t="n"/>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="G20" s="33" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="H20" s="8" t="n"/>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="G21" s="33" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="H21" s="8" t="n"/>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="G22" s="33" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="H22" s="8" t="n"/>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Name: (E)김감기 · Date of birth: 19870202</t>
+          <t>The test patient: name + date of birth</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="E23" s="28" t="inlineStr">
         <is>
-          <t>Searching (E)김감기 with 19870202 again returned RX-20260930-011 — 대기 중 · (E)김감기 · 1987-02-02 · **서류 1장** · 등록자 May park — and RX-20260930-004 unchanged at 서류 0장. The document added in step 8 is counted on the case that received it and on no other.</t>
+          <t>Searching the test patient with 19870202 again returned RX-20260930-011 — 대기 중 · the test patient · 1987-02-02 · **서류 1장** · 등록자 May park — and RX-20260930-004 unchanged at 서류 0장. The document added in step 8 is counted on the case that received it and on no other.</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="G23" s="33" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="H23" s="8" t="n"/>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="G24" s="33" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="H24" s="8" t="n"/>
@@ -2592,7 +2592,7 @@
     <row r="2">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>단계 4 — 남이 올린 건의 상세 · 등록자 안내와 환자 정보(성명 (E)김감기)</t>
+          <t>단계 4 — 남이 올린 건의 상세 · 등록자 안내와 환자 정보</t>
         </is>
       </c>
     </row>
